--- a/_Rarzrabotki/notebook/specs/2026-10-02-ekonomiya-materialiv-ss-irc-DODATOK.xlsx
+++ b/_Rarzrabotki/notebook/specs/2026-10-02-ekonomiya-materialiv-ss-irc-DODATOK.xlsx
@@ -10,8 +10,9 @@
     <sheet name="З чого складається економія" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Будинки" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="По назвах" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Куди пішли матеріали" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Порівняння економії" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Не списано на жоден будинок" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Куди пішли матеріали" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Порівняння економії" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.###"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +53,10 @@
     <font>
       <b val="1"/>
       <color rgb="001B7F4B"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -89,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -106,6 +111,38 @@
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -10066,6 +10103,3520 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:S68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="95" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Позиції кошторису, не списані на жоден будинок: 254 674,40 грн (15 м №1–№6 — 159 350,40 грн, 30 м №1–№2 — 95 324,00 грн)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Сума — норма кошторису (СС) на всі будинки групи за цінами СС з ПДВ: 15 м — 6 будинків, 30 м №1–№2 — 2 будинки. У записці й на аркуші «З чого складається економія» це рядок «Позиції кошторису, не списані на жоден будинок» (там — зі знаком мінус, як економія). Закупівлі — ERP по 30.09.2026 на весь проєкт (13 будинків); списання й залишки — бухоблік на 02.10.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Уся сума 254 674,40 грн входить в імовірну економію (1 109 285,32 грн) і не входить у нижню межу (494 923,85 грн). Точно не економія — 19 656,40 грн: ту саму позицію списано під іншою загальною назвою. Решта 235 018,00 грн — економія лише за умови, що цих позицій у будинках фізично немає.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>1. Що з цими позиціями і чи це економія</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Що з позицією</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>15 м: позицій</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>15 м: грн</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30 м №1–№2: позицій</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30 м №1–№2: грн</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Разом: позицій</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Разом: грн</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Чи це економія</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Що це означає</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>117804</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>45212</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>163016</v>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>так, якщо позиції в будинку немає</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>Окремих закупівель під цими назвами немає (ERP по 30.09.2026). Якщо позиції в будинку немає, вона в кошторисі зайва й економія реальна; якщо її поставлено в комплекті з іншим матеріалом — це не економія. Підтвердити може лише виробництво.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>закуплено, але на будинки цього типу не списано</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>28722</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>43280</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>72002</v>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>так, якщо матеріалу в будинку немає; якщо він є — це недосписання</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Під цією загальною назвою є закупівлі для проєкту, але на будинки цього типу нічого не списано: матеріал списано на будинки іншого типу, він лежить на складах або закуплено інший виріб. Якщо матеріал у будинках є, а його не списано, — це недосписання, а не економія.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>списано під іншою загальною назвою</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>12824.4</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>6832</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>19656.4</v>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>ні</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>Ту саму позицію списано під іншою загальною назвою; її вартість уже стоїть в іншому рядку (перевитрата за іншою назвою або «поза кошторисом»), і в загальній різниці з нормою вони взаємно гасяться.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>159350.4</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>95324</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>254674.4</v>
+      </c>
+      <c r="H10" s="19" t="inlineStr"/>
+      <c r="I10" s="19" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Позиції «Клей (15 м)», «Обрізні диски (30 м)» розділено між двома категоріями за кількістю, тому позицій за категоріями більше, ніж 28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>2. Розшифровка по позиціях</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Загальна назва</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Позиція в кошторисі (етап)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Од.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Норма на будинок, к-сть</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Ціна за кошторисом, грн</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Норма на будинок, грн</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Будинків</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Не списано: к-сть (норма на всі будинки)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Не списано: сума, грн</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>у т. ч. списано під іншою назвою, грн</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Що з позицією</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Закуплено на проєкт (ERP): к-сть</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Од. закупівлі</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Закуплено: грн з ПДВ</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Списано на будинки іншого типу та 30 м №3</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>На складі проєкту: к-сть</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>На складі проєкту: грн з ПДВ</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>Факти й що потрібно для підтвердження</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>15 м №1–№6 (6 будинків)</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="22" t="n"/>
+      <c r="K15" s="22" t="n"/>
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="22" t="n"/>
+      <c r="N15" s="22" t="n"/>
+      <c r="O15" s="22" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="22" t="n"/>
+      <c r="R15" s="22" t="n"/>
+      <c r="S15" s="23" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Бойлер 82</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Бойлер на 82 л (сантехніка)</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>9200</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>9200</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>55200</v>
+      </c>
+      <c r="K16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P16" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S16" s="16" t="inlineStr">
+        <is>
+          <t>У кошторисі на будинок два бойлери: «Бойлер на 82 л» — 9 200,00 грн і «Бойлер на 30 л» — 5 600,00 грн. Закуплено лише бойлери 30 л — 13 шт. (ІБ00-003089 від 10.07.2026 — 6 шт.; ІБ00-004089 від 27.08.2026 — 7 шт.); списано: 15 м №1–№6 — по 1 шт. (разом 6 шт.); 30 м №1–№2 — по 1 шт. (разом 2 шт.); на складі проєкту — 5 шт. Бойлера 82 л на будинках і складах IRC немає під жодною назвою. Якщо бойлер 82 л у будинку не потрібен, позиція в кошторисі зайва й економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Інформаційний банер</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Інформаційний банер зовнішній (додаткова комплектація)</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>6400</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>6400</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>38400</v>
+      </c>
+      <c r="K17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R17" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S17" s="16" t="inlineStr">
+        <is>
+          <t>Окремої закупівлі немає; банера на будинках і складах IRC немає під жодною назвою. Якщо банер не виготовляли (або його надав замовник), позиція в кошторисі зайва й економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Підвіконик ПВХ</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Підвіконик ПВХ (вікна/двері)</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>573</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>1719</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>10314</v>
+      </c>
+      <c r="K18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P18" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S18" s="16" t="inlineStr">
+        <is>
+          <t>Окремої закупівлі немає; підвіконь на будинках і складах IRC немає під жодною назвою. Вікна закуплено за м² без окремих рядків підвіконь: якщо підвіконня входили в постачання вікон — це не економія; якщо підвіконь у будинках немає — економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Сигналізація виявлення диму</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Сигналізація виявлення диму (додаткова комплектація)</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>340</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="J19" s="18" t="n">
+        <v>6120</v>
+      </c>
+      <c r="K19" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M19" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O19" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P19" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q19" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R19" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S19" s="16" t="inlineStr">
+        <is>
+          <t>Окремої закупівлі немає; датчиків диму на будинках і складах IRC немає під жодною назвою. Якщо їх не встановлювали (або їх надав замовник), позиція в кошторисі зайва й економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Труба гофра</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Труба ПВХ гнучка 20мм (електрика/підігрів)</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P20" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S20" s="16" t="inlineStr">
+        <is>
+          <t>Окремої закупівлі немає; гофротруби на будинках і складах IRC немає під жодною назвою. Якщо кабель прокладали без гофротруби, позиція в кошторисі зайва й економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Підключення емкості</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Підключення емкості (сантехніка)</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>208</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>208</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" s="18" t="n">
+        <v>1248</v>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M21" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O21" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P21" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q21" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R21" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S21" s="16" t="inlineStr">
+        <is>
+          <t>Окремої закупівлі немає. Імовірно, ємність підключено муфтою ПЕ 25×3/4 (загальна назва «Муфта», у кошторисі її немає): таких муфт закуплено 10 шт. — стільки ж, скільки ємностей (10 шт.); списано по одній: 15 м №1, №2, №4, №5, №6 — по 1 шт. (разом 5 шт.); на 15 м №3 — немає. Якщо підключення виконано цією муфтою — це не економія; якщо підключення не потрібне — економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Сантехнічна редукція</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Сантехнічна редукція 50х32 (сантехніка)</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>87</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <v>87</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" s="18" t="n">
+        <v>522</v>
+      </c>
+      <c r="K22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P22" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S22" s="16" t="inlineStr">
+        <is>
+          <t>Окремої закупівлі немає; редукцій і переходів 50×32 на будинках і складах IRC немає. Якщо редукція не потрібна (змінено схему зливу), позиція в кошторисі зайва й економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Грунт</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Грунт під клей (оздоблення)</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>226</v>
+      </c>
+      <c r="G23" s="18" t="n">
+        <v>4520</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="24" t="n">
+        <v>120</v>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>27120</v>
+      </c>
+      <c r="K23" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="16" t="inlineStr">
+        <is>
+          <t>закуплено, але на будинки цього типу не списано</t>
+        </is>
+      </c>
+      <c r="M23" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="N23" s="17" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="O23" s="18" t="n">
+        <v>39235.39</v>
+      </c>
+      <c r="P23" s="16" t="inlineStr">
+        <is>
+          <t>30 м №1 — 10 кг</t>
+        </is>
+      </c>
+      <c r="Q23" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="R23" s="18" t="n">
+        <v>33630.33</v>
+      </c>
+      <c r="S23" s="16" t="inlineStr">
+        <is>
+          <t>Закуплено «Грунт 10кг» — 70 кг, тобто 7 відер по 10 кг, по 560,51 грн/кг з ПДВ (21.08.2026, КОМЕРЦІЙНА ПІДЛОГА ТОВ); у кошторисі — 226,00 грн/кг. На будинки 15 м ґрунт не списано; списано: 30 м №1 — 10 кг; на складі проєкту — 60 кг (33 630,33 грн). Якщо підлогу 15 м ґрунтували, а ґрунт не списано, — це недосписання, а не економія.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Клей</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Клей монтажнй білий (оздоблення)</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>267</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <v>1068</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="J24" s="18" t="n">
+        <v>6408</v>
+      </c>
+      <c r="K24" s="18" t="n">
+        <v>4806</v>
+      </c>
+      <c r="L24" s="16" t="inlineStr">
+        <is>
+          <t>частково (18 із 24 шт.) списано під іншою загальною назвою; решта — закуплено, але на будинки цього типу не списано</t>
+        </is>
+      </c>
+      <c r="M24" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="N24" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="O24" s="18" t="n">
+        <v>4304</v>
+      </c>
+      <c r="P24" s="16" t="inlineStr">
+        <is>
+          <t>30 м №2 — 2 шт.</t>
+        </is>
+      </c>
+      <c r="Q24" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="R24" s="18" t="n">
+        <v>2306</v>
+      </c>
+      <c r="S24" s="16" t="inlineStr">
+        <is>
+          <t>Монтажний клей Lacrysil білий списано під загальною назвою «Піна клей»: 15 м №1–№6 — по 3 шт. (разом 18 шт.), 2 000,00 грн без ПДВ; це та сама позиція під іншою загальною назвою — не економія (4 806,00 грн за нормою). Решту норми — 6 шт. (1 602,00 грн) — не списано. Під назвою «клей» закуплено 25 шт. (25.08.2026 Буд-Маг ТОВ — «Клей універсальний монтажний "Шалена липучка" Лакрисіл 0,4кг», 24 шт.; 26.08.2026 Синявська Олена Олександрівна — «Клей монтажний, 12 кг», 1 шт.); списано: 30 м №2 — 2 шт.; на складі проєкту — 7 шт. (2 306,00 грн).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Дозатор рідкого мила</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Дозатор рідкого мила (додаткова комплектація)</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>587</v>
+      </c>
+      <c r="G25" s="18" t="n">
+        <v>587</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" s="18" t="n">
+        <v>3522</v>
+      </c>
+      <c r="K25" s="18" t="n">
+        <v>3522</v>
+      </c>
+      <c r="L25" s="16" t="inlineStr">
+        <is>
+          <t>списано під іншою загальною назвою</t>
+        </is>
+      </c>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O25" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P25" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R25" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S25" s="16" t="inlineStr">
+        <is>
+          <t>Списано під загальною назвою «Диспенсер рідкого мила»: 6 шт. на 2 340,58 грн (ця сума — у рядку «Списано матеріалів, яких немає в кошторисі»); це та сама позиція під іншою загальною назвою — не економія.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>З'єднувач компресійний</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>З'єднувач компресійний 25 мм (сантехніка)</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="G26" s="18" t="n">
+        <v>389.4</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="J26" s="18" t="n">
+        <v>2336.4</v>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>2336.4</v>
+      </c>
+      <c r="L26" s="16" t="inlineStr">
+        <is>
+          <t>списано під іншою загальною назвою</t>
+        </is>
+      </c>
+      <c r="M26" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="N26" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="O26" s="18" t="n">
+        <v>8226.200000000001</v>
+      </c>
+      <c r="P26" s="16" t="inlineStr">
+        <is>
+          <t>30 м №1–№2 — по 4 шт. (разом 8 шт.)</t>
+        </is>
+      </c>
+      <c r="Q26" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="R26" s="18" t="n">
+        <v>6131</v>
+      </c>
+      <c r="S26" s="16" t="inlineStr">
+        <is>
+          <t>Компресійні з'єднувачі ПЕ 25 списано на 15 м №1–№6 під загальною назвою «Муфта»: «Муфта ПЕ 25 затискна» — 12 шт.; «Муфта ПЕ 25*1/2 В» — 8 шт. (разом 20 шт. при нормі 18 шт., 1 612,00 грн без ПДВ); це та сама позиція під іншою загальною назвою — не економія. Під назвою «З'єднувач компресійний» закуплено інші вироби: 27.08.2026 РОМСТАЛ УКРАЇНА ТОВ — «З’єднання з амереканкою РР-R D=20 ммх1/2 В», 14 шт.; 27.08.2026 РОМСТАЛ УКРАЇНА ТОВ — «З’єднання з амереканкою РР-R D=20 ммх1/2 Н», 14 шт.; 28.08.2026 Синявська Олена Олександрівна — «Профіль Т-образний з’єднувальний АТ-20мм 2,7м(срібло)», 5 шт.. З них списано: 30 м №1–№2 — по 4 шт. (разом 8 шт.); на складі проєкту — 25 шт. (6 131,00 грн), серед них 5 шт. — профіль Т-подібний для підлоги.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Дозатор рушників</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>Дозатор рушників (додаткова комплектація)</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>360</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>360</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>2160</v>
+      </c>
+      <c r="K27" s="18" t="n">
+        <v>2160</v>
+      </c>
+      <c r="L27" s="16" t="inlineStr">
+        <is>
+          <t>списано під іншою загальною назвою</t>
+        </is>
+      </c>
+      <c r="M27" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O27" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P27" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q27" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R27" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S27" s="16" t="inlineStr">
+        <is>
+          <t>Списано під загальною назвою «Диспенсер рушників»: 6 шт. на 2 866,18 грн (ця сума — у рядку «Списано матеріалів, яких немає в кошторисі»); це та сама позиція під іншою загальною назвою — не економія.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>Разом 15 м</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="20" t="n"/>
+      <c r="J28" s="21" t="n">
+        <v>159350.4</v>
+      </c>
+      <c r="K28" s="21" t="n">
+        <v>12824.4</v>
+      </c>
+      <c r="L28" s="19" t="n"/>
+      <c r="M28" s="20" t="n"/>
+      <c r="N28" s="20" t="n"/>
+      <c r="O28" s="21" t="n">
+        <v>51765.59</v>
+      </c>
+      <c r="P28" s="19" t="n"/>
+      <c r="Q28" s="20" t="n"/>
+      <c r="R28" s="21" t="n">
+        <v>42067.33</v>
+      </c>
+      <c r="S28" s="19" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>30 м №1–№2 (2 будинки)</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="22" t="n"/>
+      <c r="K29" s="22" t="n"/>
+      <c r="L29" s="23" t="n"/>
+      <c r="M29" s="22" t="n"/>
+      <c r="N29" s="22" t="n"/>
+      <c r="O29" s="22" t="n"/>
+      <c r="P29" s="23" t="n"/>
+      <c r="Q29" s="22" t="n"/>
+      <c r="R29" s="22" t="n"/>
+      <c r="S29" s="23" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Бойлер 82</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Бойлер на 82 л (сантехніка)</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>9200</v>
+      </c>
+      <c r="G30" s="18" t="n">
+        <v>9200</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="18" t="n">
+        <v>18400</v>
+      </c>
+      <c r="K30" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L30" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M30" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O30" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q30" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R30" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S30" s="16" t="inlineStr">
+        <is>
+          <t>У кошторисі на будинок два бойлери: «Бойлер на 82 л» — 9 200,00 грн і «Бойлер на 30 л» — 5 600,00 грн. Закуплено лише бойлери 30 л — 13 шт. (ІБ00-003089 від 10.07.2026 — 6 шт.; ІБ00-004089 від 27.08.2026 — 7 шт.); списано: 15 м №1–№6 — по 1 шт. (разом 6 шт.); 30 м №1–№2 — по 1 шт. (разом 2 шт.); на складі проєкту — 5 шт. Бойлера 82 л на будинках і складах IRC немає під жодною назвою. Якщо бойлер 82 л у будинку не потрібен, позиція в кошторисі зайва й економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Інформаційний банер</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Інформаційний банер зовнішній (додаткова комплектація)</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>6400</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>6400</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="18" t="n">
+        <v>12800</v>
+      </c>
+      <c r="K31" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L31" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M31" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O31" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q31" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R31" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S31" s="16" t="inlineStr">
+        <is>
+          <t>Окремої закупівлі немає; банера на будинках і складах IRC немає під жодною назвою. Якщо банер не виготовляли (або його надав замовник), позиція в кошторисі зайва й економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Підвіконик ПВХ</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Підвіконик ПВХ (вікна/двері)</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>573</v>
+      </c>
+      <c r="G32" s="18" t="n">
+        <v>3438</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="J32" s="18" t="n">
+        <v>6876</v>
+      </c>
+      <c r="K32" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L32" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M32" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O32" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P32" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R32" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S32" s="16" t="inlineStr">
+        <is>
+          <t>Окремої закупівлі немає; підвіконь на будинках і складах IRC немає під жодною назвою. Вікна закуплено за м² без окремих рядків підвіконь: якщо підвіконня входили в постачання вікон — це не економія; якщо підвіконь у будинках немає — економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>Труба гофра</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Труба ПВХ гнучка гофр. 20мм (електрика/підігрів)</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="G33" s="18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="24" t="n">
+        <v>200</v>
+      </c>
+      <c r="J33" s="18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K33" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L33" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M33" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N33" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O33" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P33" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q33" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R33" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S33" s="16" t="inlineStr">
+        <is>
+          <t>Окремої закупівлі немає; гофротруби на будинках і складах IRC немає під жодною назвою. Якщо кабель прокладали без гофротруби, позиція в кошторисі зайва й економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Сигналізація виявлення диму</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Сигналізація виявлення диму (додаткова комплектація)</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>340</v>
+      </c>
+      <c r="G34" s="18" t="n">
+        <v>1360</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J34" s="18" t="n">
+        <v>2720</v>
+      </c>
+      <c r="K34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P34" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R34" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S34" s="16" t="inlineStr">
+        <is>
+          <t>Окремої закупівлі немає; датчиків диму на будинках і складах IRC немає під жодною назвою. Якщо їх не встановлювали (або їх надав замовник), позиція в кошторисі зайва й економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Підключення емкості</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>Підключення емкості до труби ПЕ (сантехніка)</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>208</v>
+      </c>
+      <c r="G35" s="18" t="n">
+        <v>208</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" s="18" t="n">
+        <v>416</v>
+      </c>
+      <c r="K35" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="16" t="inlineStr">
+        <is>
+          <t>не закуплено й не списано</t>
+        </is>
+      </c>
+      <c r="M35" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O35" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P35" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q35" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R35" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S35" s="16" t="inlineStr">
+        <is>
+          <t>Окремої закупівлі немає. Імовірно, ємність підключено муфтою ПЕ 25×3/4 (загальна назва «Муфта», у кошторисі її немає): таких муфт закуплено 10 шт. — стільки ж, скільки ємностей (10 шт.); списано по одній: 30 м №1 — 1 шт.; на 30 м №2 — немає. Якщо підключення виконано цією муфтою — це не економія; якщо підключення не потрібне — економія реальна.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Стілець</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>Стільці для відвідувачів і персоналу (додаткова комплектація)</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G36" s="18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="J36" s="18" t="n">
+        <v>24000</v>
+      </c>
+      <c r="K36" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L36" s="16" t="inlineStr">
+        <is>
+          <t>закуплено, але на будинки цього типу не списано</t>
+        </is>
+      </c>
+      <c r="M36" s="24" t="n">
+        <v>34</v>
+      </c>
+      <c r="N36" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="O36" s="18" t="n">
+        <v>29948.4</v>
+      </c>
+      <c r="P36" s="16" t="inlineStr">
+        <is>
+          <t>15 м №1–№6 — по 3 шт. (разом 18 шт.)</t>
+        </is>
+      </c>
+      <c r="Q36" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="R36" s="18" t="n">
+        <v>15429.4</v>
+      </c>
+      <c r="S36" s="16" t="inlineStr">
+        <is>
+          <t>Закуплено 18 шт. 17.07.2026 (РОЗЕТКА ТОВ, підрозділ «МД IRC 2026 15 м (МД IRC 2026)») — списано: 15 м №1–№6 — по 3 шт. (разом 18 шт.). Ще 16 шт. закуплено 28.09.2026 (Епіцентр К ТОВ) — стільки ж, скільки норма 30 м №1–№2 (8 × 2); вони на складі проєкту — 15 429,40 грн разом із додатковими витратами 1 519,00 грн (ІБ00-000392 від 28.09.2026). Якщо стільці передано на 30 м №1–№2, а не списано, — це недосписання, а не економія.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Дошка</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>Дошка 20*100 (каркас)</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>19500</v>
+      </c>
+      <c r="G37" s="18" t="n">
+        <v>3120</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" s="25" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J37" s="18" t="n">
+        <v>6240</v>
+      </c>
+      <c r="K37" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L37" s="16" t="inlineStr">
+        <is>
+          <t>закуплено, але на будинки цього типу не списано</t>
+        </is>
+      </c>
+      <c r="M37" s="25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="O37" s="18" t="n">
+        <v>33329.7</v>
+      </c>
+      <c r="P37" s="16" t="inlineStr">
+        <is>
+          <t>15 м №1–№6 — по 0,08 м³ (разом 0,48 м³)</t>
+        </is>
+      </c>
+      <c r="Q37" s="25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R37" s="18" t="n">
+        <v>25920</v>
+      </c>
+      <c r="S37" s="16" t="inlineStr">
+        <is>
+          <t>Закуплено: 13.07.2026 СТАРТВУД ТОВ — «Дошка 20*100*3000», 0,48 м³; 25.09.2026 РУФ-СТАР ТОВ — «Дошка 20*100*3000», 1,80 м³; списано: 15 м №1–№6 — по 0,08 м³ (разом 0,48 м³); на складі проєкту — 1,80 м³ (25 920,00 грн). На 30 м №1–№2 (норма 0,16 м³ на будинок) дошку не списано. Якщо дошку на 30 м використано, а не списано, — це недосписання, а не економія.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Вітробарєр</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>Вітробарєр (оздоблення)</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="n">
+        <v>81.97499999999999</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>29.00884415980482</v>
+      </c>
+      <c r="G38" s="18" t="n">
+        <v>2378</v>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" s="25" t="n">
+        <v>163.95</v>
+      </c>
+      <c r="J38" s="18" t="n">
+        <v>4756</v>
+      </c>
+      <c r="K38" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L38" s="16" t="inlineStr">
+        <is>
+          <t>закуплено, але на будинки цього типу не списано</t>
+        </is>
+      </c>
+      <c r="M38" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="N38" s="17" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="O38" s="18" t="n">
+        <v>8400</v>
+      </c>
+      <c r="P38" s="16" t="inlineStr">
+        <is>
+          <t>15 м №1–№6 — по 75 м² (разом 450 м²)</t>
+        </is>
+      </c>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R38" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S38" s="16" t="inlineStr">
+        <is>
+          <t>Закуплено 10.07.2026 Буд-Маг ТОВ — «Мембрана дифузійна», 300 м². На 15 м №1–№6 списано: «Мембрана дифузійна» — 300 м²; «Мембрана Strotex basic (вітро-гідробар'єр) 1300 супердифузійна (1,5 х 50)» — 150 м² (мембрану Strotex отримано з інших складів, серед закупівель IRC її немає). На 30 м №1–№2 під цією назвою не списано нічого, але під назвою «Мембрана» списано супердифузійну мембрану: 30 м №1 — 2 рул.; 30 м №2 — 3 рул. (по 75 м²). У кошторисі 30 м назва «Мембрана» — окремий рядок «Паро-гідро бар'єр» (2,80 рул. на будинок), тому за даними обліку не видно, чи ці рулони замінили вітробар'єр. Якщо так — це не економія.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Хомут</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>Хомут для труб PP-R д20 (сантехніка)</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="G39" s="18" t="n">
+        <v>1980</v>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="J39" s="18" t="n">
+        <v>3960</v>
+      </c>
+      <c r="K39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L39" s="16" t="inlineStr">
+        <is>
+          <t>закуплено, але на будинки цього типу не списано</t>
+        </is>
+      </c>
+      <c r="M39" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="N39" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="O39" s="18" t="n">
+        <v>480.05</v>
+      </c>
+      <c r="P39" s="16" t="inlineStr">
+        <is>
+          <t>15 м №1, №2, №3, №5, №6 — по 2 шт. (разом 10 шт.)</t>
+        </is>
+      </c>
+      <c r="Q39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R39" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S39" s="16" t="inlineStr">
+        <is>
+          <t>Хомута для труб PP-R д20 не закуплено. Під назвою «Хомут» закуплено інший виріб — 23.07.2026 Синявська Олена Олександрівна — «Хомут 4 з дюбелем та шпилькою М10(110-118 мм)», 6 шт.; на 15 м списано: «Хомут 4 з дюбелем та шпилькою М10(110-118 мм)» — 15 м №1–№3 — по 2 шт. (разом 6 шт.); «Хомут з дюбелем та шпилькою 1 1/2 47-51 9з дюбелем та шпилькою М8)» — 15 м №5–№6 — по 2 шт. (разом 4 шт.). На складі 30 м №1 — 3 хомути на каналізаційну трубу 110 мм (188,35 грн), не списано. На складах 30 м лежать кліпси PP-R 20 (загальна назва «кліпса»): 30 м №1 — 20 шт.; 30 м №2 — 10 шт., не списано — імовірно, це кріплення труб PP-R. Якщо їх використано, а не списано, — це недосписання, а не економія.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Газ зварювальний</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>Мікс балон (каркас)</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>1276</v>
+      </c>
+      <c r="G40" s="18" t="n">
+        <v>1276</v>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" s="18" t="n">
+        <v>2552</v>
+      </c>
+      <c r="K40" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L40" s="16" t="inlineStr">
+        <is>
+          <t>закуплено, але на будинки цього типу не списано</t>
+        </is>
+      </c>
+      <c r="M40" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="N40" s="17" t="inlineStr">
+        <is>
+          <t>бал.</t>
+        </is>
+      </c>
+      <c r="O40" s="18" t="n">
+        <v>10416</v>
+      </c>
+      <c r="P40" s="16" t="inlineStr">
+        <is>
+          <t>15 м №1–№6 — по 0,50 шт. (разом 3 шт.)</t>
+        </is>
+      </c>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R40" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S40" s="16" t="inlineStr">
+        <is>
+          <t>Закуплено 24.07.2026 Шеврон-газ ТОВ — «Суміш зварювальна МІКС-1 бал.40л.», 8 бал. на склад «ІС Основной склад»; усі балони переміщено на інші об'єкти: «ІС Кривий ріг Виробничий» — 7; «СТІЛ Чорноморськ» — 1. На 15 м списано газ з інших партій. На 30 м №1–№2 газу не списано, але списано зварювальний дріт 1,2 мм: 30 м №1 — 10 кг; 30 м №2 — 25 кг. Якщо каркаси 30 м №1–№2 зварювали напівавтоматом у захисному газі, газ використано, але не списано, — це недосписання, а не економія.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>Обрізні диски</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>Обрізний диск 230 мм (каркас)</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="G41" s="18" t="n">
+        <v>768</v>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="J41" s="18" t="n">
+        <v>1536</v>
+      </c>
+      <c r="K41" s="18" t="n">
+        <v>672</v>
+      </c>
+      <c r="L41" s="16" t="inlineStr">
+        <is>
+          <t>частково (7 із 16 шт.) списано під іншою загальною назвою; решта — закуплено, але на будинки цього типу не списано</t>
+        </is>
+      </c>
+      <c r="M41" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="N41" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="O41" s="18" t="n">
+        <v>3457.44</v>
+      </c>
+      <c r="P41" s="16" t="inlineStr">
+        <is>
+          <t>15 м №1 — 2 шт.; 30 м №3 — 3 шт.</t>
+        </is>
+      </c>
+      <c r="Q41" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R41" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S41" s="16" t="inlineStr">
+        <is>
+          <t>Відрізні круги 230 мм списано під загальною назвою «МШП»: 30 м №1 — 5 шт.; 30 м №2 — 2 шт., 336,14 грн без ПДВ; це та сама позиція під іншою загальною назвою — не економія (672,00 грн за нормою). Решту норми — 9 шт. (864,00 грн) — не списано. Під назвою «Обрізні диски» закуплено 20.07.2026 ТПК ПАРТНЕР-3 ТОВ — «Відрізний диск Standard Inox 230x1,9мм арт.2608601514», 60 шт. (склад «ІБ_МШП»); списано: 15 м №1 — 2 шт.; 30 м №3 — 3 шт..</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Замок навісний</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>Замок навісний (каркас)</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>350</v>
+      </c>
+      <c r="G42" s="18" t="n">
+        <v>350</v>
+      </c>
+      <c r="H42" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="18" t="n">
+        <v>700</v>
+      </c>
+      <c r="K42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="16" t="inlineStr">
+        <is>
+          <t>закуплено, але на будинки цього типу не списано</t>
+        </is>
+      </c>
+      <c r="M42" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="N42" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="O42" s="18" t="n">
+        <v>1494</v>
+      </c>
+      <c r="P42" s="16" t="inlineStr">
+        <is>
+          <t>15 м №1–№6 — по 1 шт. (разом 6 шт.)</t>
+        </is>
+      </c>
+      <c r="Q42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R42" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S42" s="16" t="inlineStr">
+        <is>
+          <t>Закуплено 14.07.2026 Масюк Дмитро Сергійович — «Замок навісний», 6 шт.; списано: 15 м №1–№6 — по 1 шт. (разом 6 шт.). Ще 12 навісних замків закуплено як «МШП» (малоцінні швидкозношувані предмети). На 30 м №1–№2 замків не списано. Якщо замки на цих будинках є, — це недосписання, а не економія.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>Канал вентеляційний</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>KO100-1 Канал d100/1 (електрика/підігрів)</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>104</v>
+      </c>
+      <c r="G43" s="18" t="n">
+        <v>104</v>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="18" t="n">
+        <v>208</v>
+      </c>
+      <c r="K43" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L43" s="16" t="inlineStr">
+        <is>
+          <t>закуплено, але на будинки цього типу не списано</t>
+        </is>
+      </c>
+      <c r="M43" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="N43" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="O43" s="18" t="n">
+        <v>1856.26</v>
+      </c>
+      <c r="P43" s="16" t="inlineStr">
+        <is>
+          <t>15 м №1–№6 — по 1 шт. (разом 6 шт.)</t>
+        </is>
+      </c>
+      <c r="Q43" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R43" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S43" s="16" t="inlineStr">
+        <is>
+          <t>Закуплено 29.07.2026 ПЛАТІНУМ ЕЛЕКТРИК ТОВ — «Канал d100/1», 6 шт.; списано: 15 м №1–№6 — по 1 шт. (разом 6 шт.). На 30 м №1–№2 вентиляційний канал не списано. Якщо його встановлено, — це недосписання, а не економія.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>Кріплення ринви</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>кріплення ринви (фасад)</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="F44" s="18" t="n">
+        <v>123</v>
+      </c>
+      <c r="G44" s="18" t="n">
+        <v>2460</v>
+      </c>
+      <c r="H44" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="J44" s="18" t="n">
+        <v>4920</v>
+      </c>
+      <c r="K44" s="18" t="n">
+        <v>4920</v>
+      </c>
+      <c r="L44" s="16" t="inlineStr">
+        <is>
+          <t>списано під іншою загальною назвою</t>
+        </is>
+      </c>
+      <c r="M44" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O44" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P44" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q44" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R44" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S44" s="16" t="inlineStr">
+        <is>
+          <t>Списано під загальною назвою «Держак ринви»: 56 шт. на 6 091,90 грн (ця сума — у рядку «Списано матеріалів, яких немає в кошторисі»); це та сама позиція під іншою загальною назвою — не економія. З них 40 шт. — пластикові держаки ринви (стільки ж, скільки норма), 16 шт. — металеві держаки водостічної труби, окремого рядка для яких у кошторисі 30 м немає.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>Кутики сталеві</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>кутик 32*32 *3 (каркас)</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F45" s="18" t="n">
+        <v>41333.33333333334</v>
+      </c>
+      <c r="G45" s="18" t="n">
+        <v>620</v>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J45" s="18" t="n">
+        <v>1240</v>
+      </c>
+      <c r="K45" s="18" t="n">
+        <v>1240</v>
+      </c>
+      <c r="L45" s="16" t="inlineStr">
+        <is>
+          <t>списано під іншою загальною назвою</t>
+        </is>
+      </c>
+      <c r="M45" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N45" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O45" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P45" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q45" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R45" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S45" s="16" t="inlineStr">
+        <is>
+          <t>Списано під загальною назвою «Кутики (металопрокат)»: 18,76 м на 1 075,68 грн (ця сума — у рядку «Списано матеріалів, яких немає в кошторисі»); це та сама позиція під іншою загальною назвою — не економія. У кошторисі — «кутик 32*32 *3», в оригіналі кошторису 10 пог. м на будинок.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>Разом 30 м</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="20" t="n"/>
+      <c r="E46" s="20" t="n"/>
+      <c r="F46" s="20" t="n"/>
+      <c r="G46" s="20" t="n"/>
+      <c r="H46" s="20" t="n"/>
+      <c r="I46" s="20" t="n"/>
+      <c r="J46" s="21" t="n">
+        <v>95324</v>
+      </c>
+      <c r="K46" s="21" t="n">
+        <v>6832</v>
+      </c>
+      <c r="L46" s="19" t="n"/>
+      <c r="M46" s="20" t="n"/>
+      <c r="N46" s="20" t="n"/>
+      <c r="O46" s="21" t="n">
+        <v>89381.85000000001</v>
+      </c>
+      <c r="P46" s="19" t="n"/>
+      <c r="Q46" s="20" t="n"/>
+      <c r="R46" s="21" t="n">
+        <v>41349.4</v>
+      </c>
+      <c r="S46" s="19" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="n"/>
+      <c r="C47" s="19" t="n"/>
+      <c r="D47" s="20" t="n"/>
+      <c r="E47" s="20" t="n"/>
+      <c r="F47" s="20" t="n"/>
+      <c r="G47" s="20" t="n"/>
+      <c r="H47" s="20" t="n"/>
+      <c r="I47" s="20" t="n"/>
+      <c r="J47" s="21" t="n">
+        <v>254674.4</v>
+      </c>
+      <c r="K47" s="21" t="n">
+        <v>19656.4</v>
+      </c>
+      <c r="L47" s="19" t="n"/>
+      <c r="M47" s="20" t="n"/>
+      <c r="N47" s="20" t="n"/>
+      <c r="O47" s="21" t="n">
+        <v>141147.44</v>
+      </c>
+      <c r="P47" s="19" t="n"/>
+      <c r="Q47" s="20" t="n"/>
+      <c r="R47" s="21" t="n">
+        <v>83416.73</v>
+      </c>
+      <c r="S47" s="19" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>3. Документи закупівлі цих позицій (ERP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Закупівлі — на весь проєкт (13 будинків); колонка «Рядок розшифровки» вказує лише, до якого рядка розділу 2 належить документ, а не для яких будинків його купували.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Рядок розшифровки</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Номер</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Постачальник</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Номенклатура</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Од.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>К-сть</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Сума з ПДВ, грн</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Склад надходження</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Грунт (15 м)</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-004011</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>КОМЕРЦІЙНА ПІДЛОГА ТОВ</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>Грунт 10кг</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="H52" s="18" t="n">
+        <v>39235.39</v>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Клей (15 м)</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-004076</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>Буд-Маг ТОВ</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>Клей універсальний монтажний "Шалена липучка" Лакрисіл 0,4кг</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="H53" s="18" t="n">
+        <v>2664</v>
+      </c>
+      <c r="I53" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>Клей (15 м)</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-004068</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>Синявська Олена Олександрівна</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>Клей монтажний, 12 кг</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="18" t="n">
+        <v>1640</v>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>З'єднувач компресійний (15 м)</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-004090</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>РОМСТАЛ УКРАЇНА ТОВ</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>З’єднання з амереканкою РР-R D=20 ммх1/2 В</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="H55" s="18" t="n">
+        <v>3603.6</v>
+      </c>
+      <c r="I55" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>З'єднувач компресійний (15 м)</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-004090</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>РОМСТАЛ УКРАЇНА ТОВ</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>З’єднання з амереканкою РР-R D=20 ммх1/2 Н</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G56" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="H56" s="18" t="n">
+        <v>3687.6</v>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>З'єднувач компресійний (15 м)</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-004084</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>Синявська Олена Олександрівна</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="inlineStr">
+        <is>
+          <t>Профіль Т-образний з’єднувальний АТ-20мм 2,7м(срібло)</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="H57" s="18" t="n">
+        <v>935</v>
+      </c>
+      <c r="I57" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>Стілець (30 м)</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>17.07.2026</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-003215</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>РОЗЕТКА ТОВ</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="inlineStr">
+        <is>
+          <t>Стілець Новий Стиль Jack</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G58" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="H58" s="18" t="n">
+        <v>16038</v>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>Стілець (30 м)</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-004879</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>Епіцентр К ТОВ</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="inlineStr">
+        <is>
+          <t>Стілець Новий Стиль Jack</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G59" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="H59" s="18" t="n">
+        <v>13910.4</v>
+      </c>
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>Дошка (30 м)</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>13.07.2026</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-003077</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>СТАРТВУД ТОВ</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>Дошка 20*100*3000</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="G60" s="25" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H60" s="18" t="n">
+        <v>7409.7</v>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>Дошка (30 м)</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-004842</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="inlineStr">
+        <is>
+          <t>РУФ-СТАР ТОВ</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="inlineStr">
+        <is>
+          <t>Дошка 20*100*3000</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>м³</t>
+        </is>
+      </c>
+      <c r="G61" s="25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H61" s="18" t="n">
+        <v>25920</v>
+      </c>
+      <c r="I61" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>Вітробарєр (30 м)</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-003025</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>Буд-Маг ТОВ</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>Мембрана дифузійна</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="G62" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="H62" s="18" t="n">
+        <v>8400</v>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>Хомут (30 м)</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-003329</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>Синявська Олена Олександрівна</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>Хомут 4 з дюбелем та шпилькою М10(110-118 мм)</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G63" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H63" s="18" t="n">
+        <v>480.05</v>
+      </c>
+      <c r="I63" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>Газ зварювальний (30 м)</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>24.07.2026</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>СТ00-001054</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>Шеврон-газ ТОВ</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>Суміш зварювальна МІКС-1 бал.40л.</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>бал.</t>
+        </is>
+      </c>
+      <c r="G64" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="H64" s="18" t="n">
+        <v>10416</v>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>ІС Основной склад</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>Обрізні диски (30 м)</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>20.07.2026</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-003573</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>ТПК ПАРТНЕР-3 ТОВ</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>Відрізний диск Standard Inox 230x1,9мм арт.2608601514</t>
+        </is>
+      </c>
+      <c r="F65" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G65" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="H65" s="18" t="n">
+        <v>3457.44</v>
+      </c>
+      <c r="I65" s="17" t="inlineStr">
+        <is>
+          <t>ІБ_МШП</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>Замок навісний (30 м)</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>14.07.2026</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-003143</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Масюк Дмитро Сергійович</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>Замок навісний</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G66" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H66" s="18" t="n">
+        <v>1494</v>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>Канал вентеляційний (30 м)</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>29.07.2026</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>ІБ00-003469</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>ПЛАТІНУМ ЕЛЕКТРИК ТОВ</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>Канал d100/1</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G67" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H67" s="18" t="n">
+        <v>1856.26</v>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>ІБ _МД IRC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="19" t="inlineStr">
+        <is>
+          <t>Разом</t>
+        </is>
+      </c>
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="19" t="n"/>
+      <c r="E68" s="19" t="n"/>
+      <c r="F68" s="20" t="n"/>
+      <c r="G68" s="20" t="n"/>
+      <c r="H68" s="21" t="n">
+        <v>141147.44</v>
+      </c>
+      <c r="I68" s="20" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
@@ -10245,7 +13796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10312,7 +13863,7 @@
       <c r="D4" s="8" t="n">
         <v>394369.75</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="26" t="n">
         <v>3.491009488339118</v>
       </c>
     </row>
@@ -10333,7 +13884,7 @@
       <c r="D5" s="8" t="n">
         <v>1316572.01</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="26" t="n">
         <v>21.0739137154933</v>
       </c>
     </row>
@@ -10354,7 +13905,7 @@
       <c r="D6" s="8" t="n">
         <v>1037439.5</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="26" t="n">
         <v>9.191951076883585</v>
       </c>
     </row>
@@ -10375,7 +13926,7 @@
       <c r="D7" s="8" t="n">
         <v>1246273.49</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="26" t="n">
         <v>19.94866957118943</v>
       </c>
     </row>
@@ -10396,7 +13947,7 @@
       <c r="D8" s="8" t="n">
         <v>1109285.32</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="26" t="n">
         <v>17.7559472189777</v>
       </c>
     </row>
@@ -10417,7 +13968,7 @@
       <c r="D9" s="8" t="n">
         <v>494923.85</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="26" t="n">
         <v>7.922075231296883</v>
       </c>
     </row>
